--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536140_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536140_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,67 +807,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5226</v>
+        <v>1.711</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5226</v>
+        <v>3.221</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1.51</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5226</v>
+        <v>0.1557</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3075</v>
+        <v>-2.1515</v>
       </c>
       <c r="I5" t="n">
-        <v>1.215</v>
+        <v>2.3072</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5226</v>
+        <v>1.2316</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3075</v>
+        <v>-1.328</v>
       </c>
       <c r="L5" t="n">
-        <v>1.215</v>
+        <v>2.5596</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.0759</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.8235</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2524</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9749</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.9499</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.9648</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.2985</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.6663</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3844</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.6658</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-3.0501</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Á. MERLO</t>
+          <t>A. MERLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.615</v>
+        <v>0.2306</v>
       </c>
       <c r="E7" t="n">
-        <v>0.615</v>
+        <v>-0.3006</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.5312</v>
       </c>
       <c r="G7" t="n">
-        <v>0.615</v>
+        <v>0.6105</v>
       </c>
       <c r="H7" t="n">
-        <v>0.615</v>
+        <v>-0.971</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.5814</v>
       </c>
       <c r="J7" t="n">
-        <v>0.615</v>
+        <v>1.3536</v>
       </c>
       <c r="K7" t="n">
-        <v>0.615</v>
+        <v>0.0575</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.296</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.7431</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.0285</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.2854</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.3649</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.7698</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.9578</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1885</v>
+        <v>-1.2023</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6984</v>
+        <v>-1.7327</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.51</v>
+        <v>0.5304</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3669</v>
+        <v>-1.25</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.459</v>
+        <v>-1.4299</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0921</v>
+        <v>0.1799</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2909</v>
+        <v>-1.3205</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6355</v>
+        <v>-1.361</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3446</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0759</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8235</v>
+        <v>-0.0689</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2524</v>
+        <v>0.1394</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9749</v>
+        <v>0.585</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9499</v>
+        <v>0.585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9648</v>
+        <v>-0.5372</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2985</v>
+        <v>-0.4122</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6663</v>
+        <v>-0.125</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3844</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.6658</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.0501</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MERLO</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3844</v>
+        <v>-1.2866</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9156</v>
+        <v>-0.1923</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5312</v>
+        <v>-1.0943</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0046</v>
+        <v>-0.2017</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.586</v>
+        <v>-0.0689</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5814</v>
+        <v>-0.1328</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7385</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5575</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.296</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7431</v>
+        <v>-0.2017</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0285</v>
+        <v>-0.0689</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2854</v>
+        <v>-0.1328</v>
       </c>
       <c r="P9" t="n">
-        <v>0.39</v>
+        <v>0.195</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3649</v>
+        <v>0.195</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7698</v>
+        <v>-0.0598</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9578</v>
+        <v>-0.1923</v>
       </c>
       <c r="U9" t="n">
-        <v>0.188</v>
+        <v>0.1325</v>
       </c>
       <c r="V9" t="n">
+        <v>-1.2201</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="W9" t="n">
-        <v>0.2786</v>
-      </c>
       <c r="X9" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>J. NWANKWO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2023</v>
+        <v>-2.7776</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7327</v>
+        <v>-2.8944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5304</v>
+        <v>0.1168</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.25</v>
+        <v>-4.6707</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4299</v>
+        <v>-2.4624</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1799</v>
+        <v>-2.2083</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3205</v>
+        <v>-3.2521</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.361</v>
+        <v>-1.2995</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-1.9525</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07049999999999999</v>
+        <v>-1.4186</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0689</v>
+        <v>-1.1629</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1394</v>
+        <v>-0.2557</v>
       </c>
       <c r="P10" t="n">
         <v>0.585</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R10" t="n">
-        <v>0.585</v>
+        <v>1.5599</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5372</v>
+        <v>0.0881</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4122</v>
+        <v>-0.166</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.125</v>
+        <v>0.2541</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2866</v>
+        <v>-4.4734</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1923</v>
+        <v>-3.338</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0943</v>
+        <v>-1.1354</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2017</v>
+        <v>-2.4575</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0689</v>
+        <v>-1.0513</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1328</v>
+        <v>-1.4062</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-1.9195</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.6395</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2017</v>
+        <v>-0.538</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0689</v>
+        <v>-0.4118</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1328</v>
+        <v>-0.1262</v>
       </c>
       <c r="P11" t="n">
-        <v>0.195</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R11" t="n">
-        <v>0.195</v>
+        <v>0.9749</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0598</v>
+        <v>-0.1858</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1923</v>
+        <v>-0.4435</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1325</v>
+        <v>0.2577</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2201</v>
+        <v>-1.8301</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2201</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. NWANKWO</t>
+          <t>A. DEL CERRO MARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7776</v>
+        <v>-6.6897</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8944</v>
+        <v>-5.2893</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1168</v>
+        <v>-1.4004</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.6707</v>
+        <v>-4.6027</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4624</v>
+        <v>-0.8554</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2083</v>
+        <v>-3.7473</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2521</v>
+        <v>-2.2345</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2995</v>
+        <v>0.4471</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9525</v>
+        <v>-2.6816</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4186</v>
+        <v>-2.3682</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1629</v>
+        <v>-1.3024</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2557</v>
+        <v>-1.0658</v>
       </c>
       <c r="P12" t="n">
-        <v>0.585</v>
+        <v>-0.195</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5599</v>
+        <v>1.7549</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0881</v>
+        <v>0.654</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.166</v>
+        <v>-0.3362</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2541</v>
+        <v>0.9901</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2201</v>
+        <v>-2.546</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4986</v>
+        <v>-0.7688</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2786</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MONES RIERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,150 +1471,146 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4734</v>
+        <v>-4.100900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.338</v>
+        <v>-1.512999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1354</v>
+        <v>-2.5881</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.4575</v>
+        <v>-17.3251</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0513</v>
+        <v>-14.6527</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4062</v>
+        <v>-2.6726</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.9195</v>
+        <v>-5.491400000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6395</v>
+        <v>-3.351</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.28</v>
+        <v>-2.1405</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.538</v>
+        <v>-11.8338</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4118</v>
+        <v>-11.3016</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1262</v>
+        <v>-0.5322000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>5.8496</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9749</v>
+        <v>-9.7493</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9749</v>
+        <v>15.599</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1858</v>
+        <v>2.4277</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4435</v>
+        <v>-1.9354</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2577</v>
+        <v>4.3632</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8301</v>
+        <v>4.946999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>15.6631</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8301</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536140_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-10.7161</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DEL CERRO MARTIN</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IREN BCBADAJOZ</t>
+          <t>CLÍNICA PONFERRADA SDP</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.6897</v>
+        <v>6.9067</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.2893</v>
+        <v>4.7701</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4004</v>
+        <v>2.1365</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.6027</v>
+        <v>2.7113</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8554</v>
+        <v>1.6908</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.7473</v>
+        <v>1.0205</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.2345</v>
+        <v>1.2716</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4471</v>
+        <v>0.6726</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.6816</v>
+        <v>0.5991</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3682</v>
+        <v>1.4397</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3024</v>
+        <v>1.0182</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0658</v>
+        <v>0.4215</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.195</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7549</v>
+        <v>0.39</v>
       </c>
       <c r="S14" t="n">
-        <v>0.654</v>
+        <v>0.265</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3362</v>
+        <v>-0.3205</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9901</v>
+        <v>0.5854</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.546</v>
+        <v>5.4903</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.7688</v>
+        <v>5.7688</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7772</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1625,86 +1621,90 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. YIMBU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IREN BCBADAJOZ</t>
+          <t>CLÍNICA PONFERRADA SDP</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.100799999999998</v>
+        <v>4.0406</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.512999999999999</v>
+        <v>2.4601</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5881</v>
+        <v>1.5805</v>
       </c>
       <c r="G15" t="n">
-        <v>-17.3252</v>
+        <v>3.0676</v>
       </c>
       <c r="H15" t="n">
-        <v>-14.6527</v>
+        <v>2.8406</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6727</v>
+        <v>0.227</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.491400000000001</v>
+        <v>2.3117</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.351</v>
+        <v>2.2307</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.140499999999999</v>
+        <v>0.081</v>
       </c>
       <c r="M15" t="n">
-        <v>-11.8338</v>
+        <v>0.7559</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.3016</v>
+        <v>0.6099</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5322000000000003</v>
+        <v>0.146</v>
       </c>
       <c r="P15" t="n">
-        <v>5.8496</v>
+        <v>-0.585</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9.7493</v>
+        <v>-0.9749</v>
       </c>
       <c r="R15" t="n">
-        <v>15.599</v>
+        <v>0.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4277</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.9354</v>
+        <v>-0.0968</v>
       </c>
       <c r="U15" t="n">
-        <v>4.3632</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>4.947000000000001</v>
+        <v>1.0473</v>
       </c>
       <c r="W15" t="n">
-        <v>15.6631</v>
+        <v>1.2201</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.7161</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+        <v>-0.1727</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2536140_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9067</v>
+        <v>3.1572</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7701</v>
+        <v>-0.0658</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1365</v>
+        <v>3.2229</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7113</v>
+        <v>5.3787</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6908</v>
+        <v>5.3867</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0205</v>
+        <v>-0.008</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2716</v>
+        <v>3.2668</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6726</v>
+        <v>3.8258</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5991</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4397</v>
+        <v>2.1119</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0182</v>
+        <v>1.5609</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4215</v>
+        <v>0.551</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5599</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9499</v>
+        <v>-2.9248</v>
       </c>
       <c r="R16" t="n">
-        <v>0.39</v>
+        <v>1.7549</v>
       </c>
       <c r="S16" t="n">
-        <v>0.265</v>
+        <v>0.1684</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3205</v>
+        <v>-0.0234</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5854</v>
+        <v>0.1919</v>
       </c>
       <c r="V16" t="n">
-        <v>5.4903</v>
+        <v>-1.2201</v>
       </c>
       <c r="W16" t="n">
-        <v>5.7688</v>
+        <v>-0.3844</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2786</v>
+        <v>-0.8357</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. YIMBU</t>
+          <t>J. IJEH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0406</v>
+        <v>2.3457</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4601</v>
+        <v>0.8853</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5805</v>
+        <v>1.4604</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0676</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>2.8406</v>
+        <v>0.8929</v>
       </c>
       <c r="I17" t="n">
-        <v>0.227</v>
+        <v>-0.089</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3117</v>
+        <v>0.1185</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2307</v>
+        <v>0.078</v>
       </c>
       <c r="L17" t="n">
-        <v>0.081</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7559</v>
+        <v>0.6854</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6099</v>
+        <v>0.8149</v>
       </c>
       <c r="O17" t="n">
-        <v>0.146</v>
+        <v>-0.1295</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.39</v>
+        <v>1.1699</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5106000000000001</v>
+        <v>-0.2382</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0968</v>
+        <v>-0.4004</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.1622</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0473</v>
+        <v>0.61</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2201</v>
+        <v>1.1671</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1727</v>
+        <v>-0.5571</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>J. BOIX COLET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1572</v>
+        <v>0.2529</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0658</v>
+        <v>-0.2483</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2229</v>
+        <v>0.5012</v>
       </c>
       <c r="G18" t="n">
-        <v>5.3787</v>
+        <v>2.3204</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3867</v>
+        <v>1.9818</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.008</v>
+        <v>0.3386</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2668</v>
+        <v>2.4552</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8258</v>
+        <v>2.3987</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.0565</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1119</v>
+        <v>-0.1348</v>
       </c>
       <c r="N18" t="n">
-        <v>1.5609</v>
+        <v>-0.4169</v>
       </c>
       <c r="O18" t="n">
-        <v>0.551</v>
+        <v>0.2821</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1699</v>
+        <v>-0.195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9248</v>
+        <v>-1.9499</v>
       </c>
       <c r="R18" t="n">
         <v>1.7549</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1684</v>
+        <v>-0.7054</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0234</v>
+        <v>-0.7536</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1919</v>
+        <v>0.0483</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2201</v>
+        <v>-1.1671</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3844</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8357</v>
+        <v>-1.1671</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. IJEH</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3457</v>
+        <v>0.1615</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8853</v>
+        <v>1.7956</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4604</v>
+        <v>-1.6341</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8038999999999999</v>
+        <v>3.4388</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8929</v>
+        <v>1.1839</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.089</v>
+        <v>2.2549</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1185</v>
+        <v>3.3652</v>
       </c>
       <c r="K19" t="n">
-        <v>0.078</v>
+        <v>0.9841</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>2.3811</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6854</v>
+        <v>0.0736</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8149</v>
+        <v>0.1999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1295</v>
+        <v>-0.1262</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1699</v>
+        <v>-2.7298</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9248</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1699</v>
+        <v>0.195</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2382</v>
+        <v>0.0625</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4004</v>
+        <v>-0.4749</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1622</v>
+        <v>0.5374</v>
       </c>
       <c r="V19" t="n">
-        <v>0.61</v>
+        <v>-0.61</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1671</v>
+        <v>1.8301</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5571</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BOIX COLET</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2529</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2483</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5012</v>
+        <v>0.6559</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3204</v>
+        <v>3.2908</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9818</v>
+        <v>0.459</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3386</v>
+        <v>2.8318</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4552</v>
+        <v>3.2107</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3987</v>
+        <v>0.2626</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0565</v>
+        <v>2.9481</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1348</v>
+        <v>0.0801</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4169</v>
+        <v>0.1964</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2821</v>
+        <v>-0.1163</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.195</v>
+        <v>-2.1448</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9499</v>
+        <v>-3.8997</v>
       </c>
       <c r="R20" t="n">
         <v>1.7549</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7054</v>
+        <v>-0.8461</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7536</v>
+        <v>-0.8871</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0483</v>
+        <v>0.041</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1671</v>
+        <v>-0.3844</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8357</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1671</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1615</v>
+        <v>-1.0939</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7956</v>
+        <v>-0.3192</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6341</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4388</v>
+        <v>0.8477</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1839</v>
+        <v>0.7813</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2549</v>
+        <v>0.0664</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3652</v>
+        <v>0.1741</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9841</v>
+        <v>1.3326</v>
       </c>
       <c r="L21" t="n">
-        <v>2.3811</v>
+        <v>-1.1585</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0736</v>
+        <v>0.6736</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1999</v>
+        <v>-0.5513</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1262</v>
+        <v>1.2249</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7298</v>
+        <v>0.7799</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9248</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.195</v>
+        <v>0.7799</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0625</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4749</v>
+        <v>-0.4933</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5374</v>
+        <v>-0.1725</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.61</v>
+        <v>-2.0557</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8301</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4401</v>
+        <v>-2.0557</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-1.3691</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6559</v>
+        <v>-0.4936</v>
       </c>
       <c r="G22" t="n">
-        <v>3.2908</v>
+        <v>-0.7778</v>
       </c>
       <c r="H22" t="n">
-        <v>0.459</v>
+        <v>-0.9544</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8318</v>
+        <v>0.1766</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2107</v>
+        <v>-0.64</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2626</v>
+        <v>-0.6805</v>
       </c>
       <c r="L22" t="n">
-        <v>2.9481</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0801</v>
+        <v>-0.1378</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1964</v>
+        <v>-0.2739</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1163</v>
+        <v>0.1361</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1448</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.8997</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7549</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8461</v>
+        <v>-0.3127</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8871</v>
+        <v>-0.2355</v>
       </c>
       <c r="U22" t="n">
-        <v>0.041</v>
+        <v>-0.0772</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3844</v>
+        <v>-0.2786</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8357</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2201</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>S. SOAREZ PEREYRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0939</v>
+        <v>-3.7485</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3192</v>
+        <v>-0.5935</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-3.155</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8477</v>
+        <v>-0.9765</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7813</v>
+        <v>-2.2386</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0664</v>
+        <v>1.2621</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1741</v>
+        <v>-0.4285</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3326</v>
+        <v>-1.279</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1585</v>
+        <v>0.8505</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6736</v>
+        <v>-0.548</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5513</v>
+        <v>-0.9596</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2249</v>
+        <v>0.4116</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7799</v>
+        <v>0.39</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7799</v>
+        <v>0.39</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.4433</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4933</v>
+        <v>-0.4435</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1725</v>
+        <v>0.0002</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0557</v>
+        <v>-2.7187</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.0557</v>
+        <v>-2.9972</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3691</v>
+        <v>-5.8788</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-4.4805</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4936</v>
+        <v>-1.3983</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7778</v>
+        <v>-2.7797</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9544</v>
+        <v>2.6287</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1766</v>
+        <v>-5.4083</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.64</v>
+        <v>-3.2715</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6805</v>
+        <v>1.4761</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0405</v>
+        <v>-4.7476</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1378</v>
+        <v>0.4918</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2739</v>
+        <v>1.1526</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1361</v>
+        <v>-0.6607</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3127</v>
+        <v>0.3661</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2355</v>
+        <v>-0.2341</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0772</v>
+        <v>0.6002</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2786</v>
+        <v>-3.6602</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2786</v>
+        <v>-3.6602</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. SOAREZ PEREYRA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,235 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7485</v>
+        <v>4.689800000000004</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5935</v>
+        <v>2.5879</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.155</v>
+        <v>2.101699999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9765</v>
+        <v>17.3252</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2386</v>
+        <v>14.6527</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2621</v>
+        <v>2.6726</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4285</v>
+        <v>11.8338</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.279</v>
+        <v>11.3017</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8505</v>
+        <v>0.5321999999999996</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.548</v>
+        <v>5.491399999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9596</v>
+        <v>3.3511</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4116</v>
+        <v>2.1405</v>
       </c>
       <c r="P25" t="n">
-        <v>0.39</v>
+        <v>-5.8496</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-15.5989</v>
       </c>
       <c r="R25" t="n">
-        <v>0.39</v>
+        <v>9.7494</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4433</v>
+        <v>-1.8389</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4435</v>
+        <v>-4.3631</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0002</v>
+        <v>2.5243</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.7187</v>
+        <v>-4.9472</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2786</v>
+        <v>10.716</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.9972</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536140_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A. MORALES ROS</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-5.8788</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-4.4805</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-1.3983</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-2.7797</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.6287</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-5.4083</v>
-      </c>
-      <c r="J26" t="n">
-        <v>-3.2715</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.4761</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-4.7476</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.4918</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.1526</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-0.6607</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-0.9749</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.1699</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.3661</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.2341</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.6002</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-3.6602</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>-3.6602</v>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>play_by_play_2536140_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4.689800000000004</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2.5879</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.101699999999999</v>
-      </c>
-      <c r="G27" t="n">
-        <v>17.3252</v>
-      </c>
-      <c r="H27" t="n">
-        <v>14.6527</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.6726</v>
-      </c>
-      <c r="J27" t="n">
-        <v>11.8338</v>
-      </c>
-      <c r="K27" t="n">
-        <v>11.3017</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.5321999999999996</v>
-      </c>
-      <c r="M27" t="n">
-        <v>5.491399999999999</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.3511</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.1405</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-5.8496</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-15.5989</v>
-      </c>
-      <c r="R27" t="n">
-        <v>9.7494</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-1.8389</v>
-      </c>
-      <c r="T27" t="n">
-        <v>-4.3631</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.5243</v>
-      </c>
-      <c r="V27" t="n">
-        <v>-4.9472</v>
-      </c>
-      <c r="W27" t="n">
-        <v>10.716</v>
-      </c>
-      <c r="X27" t="n">
         <v>-15.6631</v>
       </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
